--- a/玉米大豆历史数据/玉米基差/Louisiana Basis.xlsx
+++ b/玉米大豆历史数据/玉米基差/Louisiana Basis.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corn_GulfCoastPortsLA" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,7 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="宋体"/>
@@ -52,8 +54,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -419,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1525"/>
+  <dimension ref="A1:N1526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="14"/>
@@ -35159,6 +35162,14 @@
         <v>95</v>
       </c>
     </row>
+    <row r="1526">
+      <c r="A1526" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1526" t="n">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/玉米大豆历史数据/玉米基差/Louisiana Basis.xlsx
+++ b/玉米大豆历史数据/玉米基差/Louisiana Basis.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1526"/>
+  <dimension ref="A1:O1527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="14"/>
@@ -35178,6 +35178,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1527">
+      <c r="A1527" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1527" t="n">
+        <v>78</v>
+      </c>
+      <c r="C1527" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/玉米大豆历史数据/玉米基差/Louisiana Basis.xlsx
+++ b/玉米大豆历史数据/玉米基差/Louisiana Basis.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1527"/>
+  <dimension ref="A1:O1528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="14"/>
@@ -35189,6 +35189,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1528">
+      <c r="A1528" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B1528" t="n">
+        <v>84</v>
+      </c>
+      <c r="C1528" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/玉米大豆历史数据/玉米基差/Louisiana Basis.xlsx
+++ b/玉米大豆历史数据/玉米基差/Louisiana Basis.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1528"/>
+  <dimension ref="A1:O1529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="14"/>
@@ -35200,6 +35200,17 @@
         <v>6</v>
       </c>
     </row>
+    <row r="1529">
+      <c r="A1529" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B1529" t="n">
+        <v>84</v>
+      </c>
+      <c r="C1529" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/玉米大豆历史数据/玉米基差/Louisiana Basis.xlsx
+++ b/玉米大豆历史数据/玉米基差/Louisiana Basis.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1529"/>
+  <dimension ref="A1:O1530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="14"/>
@@ -35211,6 +35211,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1530">
+      <c r="A1530" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1530" t="n">
+        <v>84</v>
+      </c>
+      <c r="C1530" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/玉米大豆历史数据/玉米基差/Louisiana Basis.xlsx
+++ b/玉米大豆历史数据/玉米基差/Louisiana Basis.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1530"/>
+  <dimension ref="A1:O1531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="14"/>
@@ -35222,6 +35222,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1531">
+      <c r="A1531" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1531" t="n">
+        <v>84</v>
+      </c>
+      <c r="C1531" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/玉米大豆历史数据/玉米基差/Louisiana Basis.xlsx
+++ b/玉米大豆历史数据/玉米基差/Louisiana Basis.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1531"/>
+  <dimension ref="A1:O1533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="14"/>
@@ -35233,6 +35233,28 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1532">
+      <c r="A1532" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1532" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="C1532" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1533" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="C1533" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/玉米大豆历史数据/玉米基差/Louisiana Basis.xlsx
+++ b/玉米大豆历史数据/玉米基差/Louisiana Basis.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1533"/>
+  <dimension ref="A1:O1534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="14"/>
@@ -35255,6 +35255,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1534">
+      <c r="A1534" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1534" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="C1534" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/玉米大豆历史数据/玉米基差/Louisiana Basis.xlsx
+++ b/玉米大豆历史数据/玉米基差/Louisiana Basis.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1534"/>
+  <dimension ref="A1:O1535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="14"/>
@@ -35266,6 +35266,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1535">
+      <c r="A1535" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1535" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="C1535" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
